--- a/cuadros/MAYO/TUCACAS.xlsx
+++ b/cuadros/MAYO/TUCACAS.xlsx
@@ -1,33 +1,112 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+  <si>
+    <t>SUCURSAL</t>
+  </si>
+  <si>
+    <t>PROVEEDOR</t>
+  </si>
+  <si>
+    <t>FACTURA</t>
+  </si>
+  <si>
+    <t>FECHA</t>
+  </si>
+  <si>
+    <t>TIPO FISCALIZACIÓN</t>
+  </si>
+  <si>
+    <t>RESPONSABLE</t>
+  </si>
+  <si>
+    <t>INCIDENCIA</t>
+  </si>
+  <si>
+    <t>TIPO DE ERROR</t>
+  </si>
+  <si>
+    <t>OBSERVACIÓN</t>
+  </si>
+  <si>
+    <t>MONTO $</t>
+  </si>
+  <si>
+    <t>F COBRADA</t>
+  </si>
+  <si>
+    <t>CLASIFICACIÓN MONTO</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>TUCACAS</t>
+  </si>
+  <si>
+    <t>SUPLIDORA EL VIGIA, C.A</t>
+  </si>
+  <si>
+    <t>6166</t>
+  </si>
+  <si>
+    <t>2026-05-01</t>
+  </si>
+  <si>
+    <t>RECEPCION</t>
+  </si>
+  <si>
+    <t>SUB DANIEL CORDERO</t>
+  </si>
+  <si>
+    <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
+  </si>
+  <si>
+    <t>TIPO A</t>
+  </si>
+  <si>
+    <t>NUMERO DE CONTROL INCORRECTO</t>
+  </si>
+  <si>
+    <t>SIN FOTO</t>
+  </si>
+  <si>
+    <t>NINGUNA</t>
+  </si>
+  <si>
+    <t>20260504112226</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,80 +125,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -407,84 +419,90 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:N1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>SUCURSAL</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>PROVEEDOR</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>FACTURA</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>FECHA</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>TIPO DE FISCALIZACION</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>RESPONSABLE</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>INCIDENCIA</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>TIPO DE ERROR</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>OBSERVACIONES</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>CLASIFICACION</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>CLASIFICACION</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>F COBRADA</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>CLASIFICACION</t>
-        </is>
+    <row r="1" spans="1:13">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/cuadros/MAYO/TUCACAS.xlsx
+++ b/cuadros/MAYO/TUCACAS.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="42">
   <si>
     <t>SUCURSAL</t>
   </si>
@@ -61,34 +61,85 @@
     <t>SUPLIDORA EL VIGIA, C.A</t>
   </si>
   <si>
-    <t>6166</t>
+    <t>ADOLFO'S VICAR, C.A</t>
+  </si>
+  <si>
+    <t>CAVA LUXOR, C.A</t>
+  </si>
+  <si>
+    <t>INVERSIONES LAS PATRONAS 2024, C,A</t>
+  </si>
+  <si>
+    <t>865</t>
   </si>
   <si>
     <t>2026-05-01</t>
   </si>
   <si>
+    <t>2026-05-02</t>
+  </si>
+  <si>
     <t>RECEPCION</t>
   </si>
   <si>
     <t>SUB DANIEL CORDERO</t>
   </si>
   <si>
+    <t xml:space="preserve">SUB DANIEL </t>
+  </si>
+  <si>
+    <t>GERENTE JUAN MEZA</t>
+  </si>
+  <si>
     <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
   </si>
   <si>
+    <t>FISCALIZACIÓN A DESTIEMPO</t>
+  </si>
+  <si>
+    <t>NO SE COMPLETA EL PROCESO DE FISCALIZACION Y SE ELIMINA.</t>
+  </si>
+  <si>
     <t>TIPO A</t>
   </si>
   <si>
+    <t>TIPO B</t>
+  </si>
+  <si>
+    <t>TIPO E</t>
+  </si>
+  <si>
     <t>NUMERO DE CONTROL INCORRECTO</t>
   </si>
   <si>
+    <t>NO CARGÓ DOCUMENTO A TIEMPO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NO CARGÓ DOCUMENTO A TIEMPO </t>
+  </si>
+  <si>
+    <t>RECEPCIÓN ELIMINADA EN APP</t>
+  </si>
+  <si>
     <t>SIN FOTO</t>
   </si>
   <si>
     <t>NINGUNA</t>
   </si>
   <si>
+    <t>RECUPERACIÓN</t>
+  </si>
+  <si>
     <t>20260504112226</t>
+  </si>
+  <si>
+    <t>20260504112705</t>
+  </si>
+  <si>
+    <t>20260504112844</t>
+  </si>
+  <si>
+    <t>20260504113615</t>
   </si>
 </sst>
 </file>
@@ -420,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
@@ -471,38 +522,161 @@
       <c r="B2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
-        <v>15</v>
+      <c r="C2">
+        <v>6166</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G2" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="H2" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I2" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2" t="s">
+        <v>35</v>
+      </c>
+      <c r="L2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3">
+        <v>13570</v>
+      </c>
+      <c r="D3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3" t="s">
+        <v>35</v>
+      </c>
+      <c r="L3" t="s">
+        <v>36</v>
+      </c>
+      <c r="M3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4">
+        <v>106794</v>
+      </c>
+      <c r="D4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" t="s">
         <v>22</v>
       </c>
-      <c r="L2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M2" t="s">
+      <c r="G4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4" t="s">
+        <v>35</v>
+      </c>
+      <c r="L4" t="s">
+        <v>36</v>
+      </c>
+      <c r="M4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" t="s">
         <v>24</v>
+      </c>
+      <c r="G5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" t="s">
+        <v>34</v>
+      </c>
+      <c r="J5">
+        <v>871.38</v>
+      </c>
+      <c r="K5" t="s">
+        <v>35</v>
+      </c>
+      <c r="L5" t="s">
+        <v>37</v>
+      </c>
+      <c r="M5" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/cuadros/MAYO/TUCACAS.xlsx
+++ b/cuadros/MAYO/TUCACAS.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="41">
   <si>
     <t>SUCURSAL</t>
   </si>
@@ -125,9 +125,6 @@
   </si>
   <si>
     <t>NINGUNA</t>
-  </si>
-  <si>
-    <t>RECUPERACIÓN</t>
   </si>
   <si>
     <t>20260504112226</t>
@@ -553,7 +550,7 @@
         <v>36</v>
       </c>
       <c r="M2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -594,7 +591,7 @@
         <v>36</v>
       </c>
       <c r="M3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -635,7 +632,7 @@
         <v>36</v>
       </c>
       <c r="M4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -673,10 +670,10 @@
         <v>35</v>
       </c>
       <c r="L5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/cuadros/MAYO/TUCACAS.xlsx
+++ b/cuadros/MAYO/TUCACAS.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="59">
   <si>
     <t>SUCURSAL</t>
   </si>
@@ -70,7 +70,22 @@
     <t>INVERSIONES LAS PATRONAS 2024, C,A</t>
   </si>
   <si>
-    <t>865</t>
+    <t>HIELO BARQUISIMETO,C.A</t>
+  </si>
+  <si>
+    <t>C.A. SUCESORA DE JOSE PUIG &amp; CIA</t>
+  </si>
+  <si>
+    <t>C.P.A BEJUMA</t>
+  </si>
+  <si>
+    <t>AGROPECUARIA PUNTA LARGA, C.A.</t>
+  </si>
+  <si>
+    <t>GALLETERA TRIGO DE ORO, C.A.</t>
+  </si>
+  <si>
+    <t>0000051800</t>
   </si>
   <si>
     <t>2026-05-01</t>
@@ -79,6 +94,9 @@
     <t>2026-05-02</t>
   </si>
   <si>
+    <t>2026-05-04</t>
+  </si>
+  <si>
     <t>RECEPCION</t>
   </si>
   <si>
@@ -91,6 +109,12 @@
     <t>GERENTE JUAN MEZA</t>
   </si>
   <si>
+    <t>GERENTE</t>
+  </si>
+  <si>
+    <t>GERENTE JUA</t>
+  </si>
+  <si>
     <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
   </si>
   <si>
@@ -100,6 +124,9 @@
     <t>NO SE COMPLETA EL PROCESO DE FISCALIZACION Y SE ELIMINA.</t>
   </si>
   <si>
+    <t>RECEPCIÓN SIN AUTORIZACIÓN DE CMF.</t>
+  </si>
+  <si>
     <t>TIPO A</t>
   </si>
   <si>
@@ -121,6 +148,15 @@
     <t>RECEPCIÓN ELIMINADA EN APP</t>
   </si>
   <si>
+    <t>SIN AUTORIZACIÓN PARA INICIAR RECEPCIÓN</t>
+  </si>
+  <si>
+    <t>SIN AUTORIZACION PARA INICIAR RECEPCIÓN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIN AUTORIZACIÓN PARA INICIAR RECEPCIÓN </t>
+  </si>
+  <si>
     <t>SIN FOTO</t>
   </si>
   <si>
@@ -137,6 +173,24 @@
   </si>
   <si>
     <t>20260504113615</t>
+  </si>
+  <si>
+    <t>20260504131121</t>
+  </si>
+  <si>
+    <t>20260504131211</t>
+  </si>
+  <si>
+    <t>20260504131403</t>
+  </si>
+  <si>
+    <t>20260504131448</t>
+  </si>
+  <si>
+    <t>20260504131610</t>
+  </si>
+  <si>
+    <t>20260504133058</t>
   </si>
 </sst>
 </file>
@@ -468,7 +522,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
@@ -523,34 +577,34 @@
         <v>6166</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F2" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="H2" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="I2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="L2" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="M2" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -564,34 +618,34 @@
         <v>13570</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G3" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="H3" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="I3" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="L3" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="M3" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -605,34 +659,34 @@
         <v>106794</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E4" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F4" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G4" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="H4" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="I4" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="L4" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="M4" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -642,38 +696,284 @@
       <c r="B5" t="s">
         <v>17</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5">
+        <v>865</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I5" t="s">
+        <v>43</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5" t="s">
+        <v>47</v>
+      </c>
+      <c r="L5" t="s">
+        <v>48</v>
+      </c>
+      <c r="M5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
         <v>18</v>
       </c>
-      <c r="D5" t="s">
+      <c r="C6">
+        <v>32184</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H6" t="s">
+        <v>39</v>
+      </c>
+      <c r="I6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6" t="s">
+        <v>47</v>
+      </c>
+      <c r="L6" t="s">
+        <v>48</v>
+      </c>
+      <c r="M6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7">
+        <v>1853933</v>
+      </c>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I7" t="s">
+        <v>45</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7" t="s">
+        <v>47</v>
+      </c>
+      <c r="L7" t="s">
+        <v>48</v>
+      </c>
+      <c r="M7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
         <v>20</v>
       </c>
-      <c r="E5" t="s">
+      <c r="C8">
+        <v>73571</v>
+      </c>
+      <c r="D8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" t="s">
+        <v>36</v>
+      </c>
+      <c r="H8" t="s">
+        <v>39</v>
+      </c>
+      <c r="I8" t="s">
+        <v>44</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8" t="s">
+        <v>47</v>
+      </c>
+      <c r="L8" t="s">
+        <v>48</v>
+      </c>
+      <c r="M8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9">
+        <v>73570</v>
+      </c>
+      <c r="D9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9" t="s">
+        <v>36</v>
+      </c>
+      <c r="H9" t="s">
+        <v>39</v>
+      </c>
+      <c r="I9" t="s">
+        <v>46</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9" t="s">
+        <v>47</v>
+      </c>
+      <c r="L9" t="s">
+        <v>48</v>
+      </c>
+      <c r="M9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
         <v>21</v>
       </c>
-      <c r="F5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="C10">
+        <v>3540</v>
+      </c>
+      <c r="D10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" t="s">
         <v>27</v>
       </c>
-      <c r="H5" t="s">
+      <c r="F10" t="s">
         <v>30</v>
       </c>
-      <c r="I5" t="s">
-        <v>34</v>
-      </c>
-      <c r="J5">
-        <v>871.38</v>
-      </c>
-      <c r="K5" t="s">
-        <v>35</v>
-      </c>
-      <c r="L5" t="s">
+      <c r="G10" t="s">
         <v>36</v>
       </c>
-      <c r="M5" t="s">
-        <v>40</v>
+      <c r="H10" t="s">
+        <v>39</v>
+      </c>
+      <c r="I10" t="s">
+        <v>46</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10" t="s">
+        <v>47</v>
+      </c>
+      <c r="L10" t="s">
+        <v>48</v>
+      </c>
+      <c r="M10" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" t="s">
+        <v>30</v>
+      </c>
+      <c r="G11" t="s">
+        <v>36</v>
+      </c>
+      <c r="H11" t="s">
+        <v>39</v>
+      </c>
+      <c r="I11" t="s">
+        <v>44</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11" t="s">
+        <v>47</v>
+      </c>
+      <c r="L11" t="s">
+        <v>48</v>
+      </c>
+      <c r="M11" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/cuadros/MAYO/TUCACAS.xlsx
+++ b/cuadros/MAYO/TUCACAS.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="70">
   <si>
     <t>SUCURSAL</t>
   </si>
@@ -85,7 +85,16 @@
     <t>GALLETERA TRIGO DE ORO, C.A.</t>
   </si>
   <si>
-    <t>0000051800</t>
+    <t>ADOLFO'S VICAR, C.A.</t>
+  </si>
+  <si>
+    <t>GALLETERA TRIGO DE ORO, C.A</t>
+  </si>
+  <si>
+    <t>AGROPECUARIA PUNTA LARGA, C.A</t>
+  </si>
+  <si>
+    <t>3540</t>
   </si>
   <si>
     <t>2026-05-01</t>
@@ -115,6 +124,9 @@
     <t>GERENTE JUA</t>
   </si>
   <si>
+    <t>SUB GENESIS COBOS</t>
+  </si>
+  <si>
     <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
   </si>
   <si>
@@ -127,6 +139,9 @@
     <t>RECEPCIÓN SIN AUTORIZACIÓN DE CMF.</t>
   </si>
   <si>
+    <t>NO FISCALIZÓ UNO O VARIOS PRODUCTOS</t>
+  </si>
+  <si>
     <t>TIPO A</t>
   </si>
   <si>
@@ -136,6 +151,9 @@
     <t>TIPO E</t>
   </si>
   <si>
+    <t>TIPO C</t>
+  </si>
+  <si>
     <t>NUMERO DE CONTROL INCORRECTO</t>
   </si>
   <si>
@@ -157,6 +175,12 @@
     <t xml:space="preserve">SIN AUTORIZACIÓN PARA INICIAR RECEPCIÓN </t>
   </si>
   <si>
+    <t>NO INGRESÓ SKU DE ROMERO EN EL APLICATIVO, 0.8KG</t>
+  </si>
+  <si>
+    <t>NÚMERO DE CONTROL INCORRECTO</t>
+  </si>
+  <si>
     <t>SIN FOTO</t>
   </si>
   <si>
@@ -191,6 +215,15 @@
   </si>
   <si>
     <t>20260504133058</t>
+  </si>
+  <si>
+    <t>HIST_20260504153829</t>
+  </si>
+  <si>
+    <t>HIST_20260504153947</t>
+  </si>
+  <si>
+    <t>HIST_20260504154107</t>
   </si>
 </sst>
 </file>
@@ -522,7 +555,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
@@ -577,34 +610,34 @@
         <v>6166</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H2" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I2" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="L2" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="M2" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -618,34 +651,34 @@
         <v>13570</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="H3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I3" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="L3" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="M3" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -659,34 +692,34 @@
         <v>106794</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E4" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G4" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="H4" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I4" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="L4" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="M4" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -700,34 +733,34 @@
         <v>865</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E5" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G5" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H5" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I5" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="L5" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="M5" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -741,34 +774,34 @@
         <v>32184</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E6" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F6" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G6" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H6" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I6" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="L6" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="M6" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -782,34 +815,34 @@
         <v>1853933</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E7" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F7" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G7" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H7" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I7" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="L7" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="M7" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -823,34 +856,34 @@
         <v>73571</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F8" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H8" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I8" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="L8" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="M8" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -864,34 +897,34 @@
         <v>73570</v>
       </c>
       <c r="D9" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E9" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F9" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G9" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H9" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I9" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="L9" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="M9" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -905,34 +938,34 @@
         <v>3540</v>
       </c>
       <c r="D10" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E10" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F10" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G10" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H10" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I10" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="J10">
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="L10" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="M10" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -942,38 +975,161 @@
       <c r="B11" t="s">
         <v>22</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11">
+        <v>51800</v>
+      </c>
+      <c r="D11" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11" t="s">
+        <v>33</v>
+      </c>
+      <c r="G11" t="s">
+        <v>40</v>
+      </c>
+      <c r="H11" t="s">
+        <v>44</v>
+      </c>
+      <c r="I11" t="s">
+        <v>50</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11" t="s">
+        <v>55</v>
+      </c>
+      <c r="L11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M11" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" t="s">
         <v>23</v>
       </c>
-      <c r="D11" t="s">
+      <c r="C12">
+        <v>13594</v>
+      </c>
+      <c r="D12" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" t="s">
+        <v>36</v>
+      </c>
+      <c r="G12" t="s">
+        <v>41</v>
+      </c>
+      <c r="H12" t="s">
+        <v>45</v>
+      </c>
+      <c r="I12" t="s">
+        <v>53</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12" t="s">
+        <v>55</v>
+      </c>
+      <c r="L12" t="s">
+        <v>56</v>
+      </c>
+      <c r="M12" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13">
+        <v>51799</v>
+      </c>
+      <c r="D13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G13" t="s">
+        <v>40</v>
+      </c>
+      <c r="H13" t="s">
+        <v>44</v>
+      </c>
+      <c r="I13" t="s">
+        <v>52</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13" t="s">
+        <v>55</v>
+      </c>
+      <c r="L13" t="s">
+        <v>56</v>
+      </c>
+      <c r="M13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" t="s">
         <v>26</v>
       </c>
-      <c r="E11" t="s">
-        <v>27</v>
-      </c>
-      <c r="F11" t="s">
-        <v>30</v>
-      </c>
-      <c r="G11" t="s">
-        <v>36</v>
-      </c>
-      <c r="H11" t="s">
-        <v>39</v>
-      </c>
-      <c r="I11" t="s">
-        <v>44</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11" t="s">
-        <v>47</v>
-      </c>
-      <c r="L11" t="s">
-        <v>48</v>
-      </c>
-      <c r="M11" t="s">
-        <v>58</v>
+      <c r="D14" t="s">
+        <v>29</v>
+      </c>
+      <c r="E14" t="s">
+        <v>30</v>
+      </c>
+      <c r="F14" t="s">
+        <v>33</v>
+      </c>
+      <c r="G14" t="s">
+        <v>37</v>
+      </c>
+      <c r="H14" t="s">
+        <v>42</v>
+      </c>
+      <c r="I14" t="s">
+        <v>54</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14" t="s">
+        <v>55</v>
+      </c>
+      <c r="L14" t="s">
+        <v>56</v>
+      </c>
+      <c r="M14" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/cuadros/MAYO/TUCACAS.xlsx
+++ b/cuadros/MAYO/TUCACAS.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="73">
   <si>
     <t>SUCURSAL</t>
   </si>
@@ -94,7 +94,10 @@
     <t>AGROPECUARIA PUNTA LARGA, C.A</t>
   </si>
   <si>
-    <t>3540</t>
+    <t>RUBROS SANARE C2, C.A.</t>
+  </si>
+  <si>
+    <t>2355</t>
   </si>
   <si>
     <t>2026-05-01</t>
@@ -184,6 +187,9 @@
     <t>SIN FOTO</t>
   </si>
   <si>
+    <t>SIN_FOTO</t>
+  </si>
+  <si>
     <t>NINGUNA</t>
   </si>
   <si>
@@ -224,6 +230,9 @@
   </si>
   <si>
     <t>HIST_20260504154107</t>
+  </si>
+  <si>
+    <t>HIST_20260504165348</t>
   </si>
 </sst>
 </file>
@@ -555,7 +564,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
@@ -610,34 +619,34 @@
         <v>6166</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="M2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -651,34 +660,34 @@
         <v>13570</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="M3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -692,34 +701,34 @@
         <v>106794</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="M4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -733,34 +742,34 @@
         <v>865</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="M5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -774,34 +783,34 @@
         <v>32184</v>
       </c>
       <c r="D6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="M6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -815,34 +824,34 @@
         <v>1853933</v>
       </c>
       <c r="D7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="M7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -856,34 +865,34 @@
         <v>73571</v>
       </c>
       <c r="D8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="M8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -897,34 +906,34 @@
         <v>73570</v>
       </c>
       <c r="D9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="M9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -938,34 +947,34 @@
         <v>3540</v>
       </c>
       <c r="D10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J10">
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="M10" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -979,34 +988,34 @@
         <v>51800</v>
       </c>
       <c r="D11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L11" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="M11" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -1020,34 +1029,34 @@
         <v>13594</v>
       </c>
       <c r="D12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L12" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="M12" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -1061,34 +1070,34 @@
         <v>51799</v>
       </c>
       <c r="D13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J13">
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L13" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="M13" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -1098,38 +1107,79 @@
       <c r="B14" t="s">
         <v>25</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14">
+        <v>3540</v>
+      </c>
+      <c r="D14" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" t="s">
+        <v>34</v>
+      </c>
+      <c r="G14" t="s">
+        <v>38</v>
+      </c>
+      <c r="H14" t="s">
+        <v>43</v>
+      </c>
+      <c r="I14" t="s">
+        <v>55</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14" t="s">
+        <v>56</v>
+      </c>
+      <c r="L14" t="s">
+        <v>58</v>
+      </c>
+      <c r="M14" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
         <v>26</v>
       </c>
-      <c r="D14" t="s">
-        <v>29</v>
-      </c>
-      <c r="E14" t="s">
+      <c r="C15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" t="s">
         <v>30</v>
       </c>
-      <c r="F14" t="s">
-        <v>33</v>
-      </c>
-      <c r="G14" t="s">
-        <v>37</v>
-      </c>
-      <c r="H14" t="s">
-        <v>42</v>
-      </c>
-      <c r="I14" t="s">
-        <v>54</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14" t="s">
-        <v>55</v>
-      </c>
-      <c r="L14" t="s">
-        <v>56</v>
-      </c>
-      <c r="M14" t="s">
-        <v>69</v>
+      <c r="E15" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" t="s">
+        <v>34</v>
+      </c>
+      <c r="G15" t="s">
+        <v>41</v>
+      </c>
+      <c r="H15" t="s">
+        <v>45</v>
+      </c>
+      <c r="I15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15" t="s">
+        <v>57</v>
+      </c>
+      <c r="L15" t="s">
+        <v>58</v>
+      </c>
+      <c r="M15" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/cuadros/MAYO/TUCACAS.xlsx
+++ b/cuadros/MAYO/TUCACAS.xlsx
@@ -2,8 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -25,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -36,6 +37,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
         <bgColor rgb="FF92D050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor rgb="FFFFC000"/>
       </patternFill>
     </fill>
   </fills>
@@ -51,12 +58,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -419,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1364,10 +1372,8 @@
           <t>COCA-COLA FEMSA DE VENEZUELA, S.A.</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>159313881</t>
-        </is>
+      <c r="C16" t="n">
+        <v>159313881</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1387,11 +1393,6 @@
       <c r="G16" t="inlineStr">
         <is>
           <t>OTRAS.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>N/A</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1418,7 +1419,72 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TUCACAS</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ADOLFO'S VICAR, C.A.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>13652</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SUB CARLOS PARACO</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ERROR DE KG EN TARA.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>TIPO C</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RESPONSABLE INGRESA TARA DE 1 CESTA DE 24KG. SE VISUALIZA Y SE VERIFICA 1 CESTA DE 2.4KG </t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>RECUPERACIÓN</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>ID_20260511142256</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/cuadros/MAYO/TUCACAS.xlsx
+++ b/cuadros/MAYO/TUCACAS.xlsx
@@ -26,24 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor rgb="FF92D050"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor rgb="FFFFC000"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -58,10 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -427,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -562,6 +548,7 @@
       <c r="M2" t="n">
         <v>20260504112226</v>
       </c>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -623,6 +610,7 @@
       <c r="M3" t="n">
         <v>20260504112705</v>
       </c>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -684,6 +672,7 @@
       <c r="M4" t="n">
         <v>20260504112844</v>
       </c>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -745,6 +734,7 @@
       <c r="M5" t="n">
         <v>20260504113615</v>
       </c>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -806,6 +796,7 @@
       <c r="M6" t="n">
         <v>20260504131211</v>
       </c>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -867,6 +858,7 @@
       <c r="M7" t="n">
         <v>20260504131403</v>
       </c>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -928,6 +920,7 @@
       <c r="M8" t="n">
         <v>20260504131448</v>
       </c>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -989,6 +982,7 @@
       <c r="M9" t="n">
         <v>20260504131610</v>
       </c>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1050,6 +1044,7 @@
       <c r="M10" t="n">
         <v>20260504133058</v>
       </c>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1111,6 +1106,7 @@
       <c r="M11" t="n">
         <v>20260504153829</v>
       </c>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1172,6 +1168,7 @@
       <c r="M12" t="n">
         <v>20260504153947</v>
       </c>
+      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1233,6 +1230,7 @@
       <c r="M13" t="n">
         <v>20260504154107</v>
       </c>
+      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1294,6 +1292,7 @@
       <c r="M14" t="n">
         <v>20260504165348</v>
       </c>
+      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1395,12 +1394,13 @@
           <t>OTRAS.</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>AL MOMENTO DE LA RECEPCIÓN, INGRESA UNA LATA DE SODA SCHWEPPES LATA 355ML AVERIADA. LA MISMA ES CANCELADA POR EL PROVEEDOR.</t>
         </is>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" t="n">
         <v>1.31</v>
       </c>
       <c r="K16" t="inlineStr">
@@ -1418,6 +1418,7 @@
           <t>ID_20260506162053</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1430,10 +1431,8 @@
           <t>ADOLFO'S VICAR, C.A.</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>13652</t>
-        </is>
+      <c r="C17" t="n">
+        <v>13652</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1465,7 +1464,7 @@
           <t xml:space="preserve">RESPONSABLE INGRESA TARA DE 1 CESTA DE 24KG. SE VISUALIZA Y SE VERIFICA 1 CESTA DE 2.4KG </t>
         </is>
       </c>
-      <c r="J17" s="2" t="n">
+      <c r="J17" t="n">
         <v>45.6</v>
       </c>
       <c r="K17" t="inlineStr">
@@ -1483,6 +1482,73 @@
           <t>ID_20260511142256</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>TUCACAS</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>INVERSIONES LAS PATRONAS 2024, C.A.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>000795</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>SUB GENESIS COBOS</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>RECEPCIÓN SIN AUTORIZACIÓN DE CMF.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>TIPO E</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SIN AUTORIZACIÓN PARA INICIAR RECEPCIÓN </t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>ID_20260513160144</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cuadros/MAYO/TUCACAS.xlsx
+++ b/cuadros/MAYO/TUCACAS.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,8 +512,10 @@
           <t>SUPLIDORA EL VIGIA, C.A</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>6166</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>6166</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -573,8 +575,10 @@
           <t>ADOLFO'S VICAR, C.A</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>13570</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>13570</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -634,8 +638,10 @@
           <t>CAVA LUXOR, C.A</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>106794</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>106794</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -695,8 +701,10 @@
           <t>INVERSIONES LAS PATRONAS 2024, C,A</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>865</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>865</t>
+        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -756,8 +764,10 @@
           <t>C.A. SUCESORA DE JOSE PUIG &amp; CIA</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>1853933</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1853933</t>
+        </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -817,8 +827,10 @@
           <t>C.P.A BEJUMA</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>73571</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>73571</t>
+        </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -878,8 +890,10 @@
           <t>C.P.A BEJUMA</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>73570</v>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>73570</t>
+        </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -939,8 +953,10 @@
           <t>AGROPECUARIA PUNTA LARGA, C.A.</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>3540</v>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3540</t>
+        </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1000,8 +1016,10 @@
           <t>GALLETERA TRIGO DE ORO, C.A.</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>51800</v>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>51800</t>
+        </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1061,8 +1079,10 @@
           <t>ADOLFO'S VICAR, C.A.</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v>13594</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>13594</t>
+        </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1122,8 +1142,10 @@
           <t>GALLETERA TRIGO DE ORO, C.A</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>51799</v>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>51799</t>
+        </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1183,8 +1205,10 @@
           <t>AGROPECUARIA PUNTA LARGA, C.A</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>3540</v>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>3540</t>
+        </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1244,8 +1268,10 @@
           <t>RUBROS SANARE C2, C.A.</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>2355</v>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2355</t>
+        </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1305,8 +1331,10 @@
           <t>HIELO BARQUISIMETO,C.A</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v>32184</v>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>32184</t>
+        </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1371,8 +1399,10 @@
           <t>COCA-COLA FEMSA DE VENEZUELA, S.A.</t>
         </is>
       </c>
-      <c r="C16" t="n">
-        <v>159313881</v>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>159313881</t>
+        </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1429,8 +1459,10 @@
           <t>ADOLFO'S VICAR, C.A.</t>
         </is>
       </c>
-      <c r="C17" t="n">
-        <v>13652</v>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>13652</t>
+        </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1492,8 +1524,10 @@
           <t>INVERSIONES LAS PATRONAS 2024, C.A.</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v>795</v>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>795</t>
+        </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1555,8 +1589,10 @@
           <t>INVERSIONES LAS PATRONAS 2024, C.A.</t>
         </is>
       </c>
-      <c r="C19" t="n">
-        <v>796</v>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>796</t>
+        </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1609,6 +1645,71 @@
       <c r="N19" t="inlineStr">
         <is>
           <t>INC_084647.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>TUCACAS</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ALIMENTOS DIFRESCA, C.A.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>212106</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>SUB CARLOS PARACO</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>RECEPCIÓN SIN AUTORIZACIÓN DE CMF.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>TIPO E</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RESPONSABLE INICIA RECEPCIÓN SIN PREVIA AUTORIZACIÓN </t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>ID_20260515131619</t>
         </is>
       </c>
     </row>
